--- a/Combined_Broker_Trades.xlsx
+++ b/Combined_Broker_Trades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_0B4E91BF92AC475D62175577F0553555E252A984" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51CD90D8-2AA5-45BF-A44C-DF5E747E225E}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_0B4E91BF92AC475D621755F360FC431BDD4C924D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D556F7B5-4EBD-4361-A599-782AFB8E61BB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Account Name</t>
   </si>
@@ -80,6 +80,36 @@
   </si>
   <si>
     <t>14-02-2025</t>
+  </si>
+  <si>
+    <t>Pasini Alberto</t>
+  </si>
+  <si>
+    <t>Alberto Pasini</t>
+  </si>
+  <si>
+    <t>504324</t>
+  </si>
+  <si>
+    <t>05-02-2026</t>
+  </si>
+  <si>
+    <t>Comgest Growth Europe EUR</t>
+  </si>
+  <si>
+    <t>Vontobel</t>
+  </si>
+  <si>
+    <t>12-02-2026</t>
+  </si>
+  <si>
+    <t>iShares STOXX Europe 600 UCITS ETF (DE) 12.02.2026 Acquisto EUR</t>
+  </si>
+  <si>
+    <t>26-02-2026</t>
+  </si>
+  <si>
+    <t>Novartis AG Namen 26.02.2026 Vendita CHF</t>
   </si>
   <si>
     <t>Chaliki Jaya Ramesh</t>
@@ -538,12 +568,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="1" max="1" width="86" customWidth="1"/>
+    <col min="2" max="2" width="54.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -699,7 +730,7 @@
         <v>24</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>1076.117</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
@@ -725,7 +756,7 @@
         <v>27</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
@@ -751,7 +782,7 @@
         <v>29</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
@@ -759,202 +790,280 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11">
-        <v>9</v>
-      </c>
-      <c r="I11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
       <c r="H12">
-        <v>500</v>
+        <v>0.1</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
         <v>43</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
       </c>
       <c r="H13">
         <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
         <v>48</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14">
+        <v>9</v>
+      </c>
+      <c r="I14" t="s">
         <v>49</v>
-      </c>
-      <c r="H14">
-        <v>1000</v>
-      </c>
-      <c r="I14" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
       </c>
       <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15">
+        <v>500</v>
+      </c>
+      <c r="I15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>50</v>
       </c>
-      <c r="G15" t="s">
+      <c r="B16" t="s">
         <v>51</v>
       </c>
-      <c r="H15">
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16">
+        <v>50</v>
+      </c>
+      <c r="I16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17">
+        <v>1000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18">
         <v>100</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I18" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 INTERNAL</oddFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 CONFIDENTIAL</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/Combined_Broker_Trades.xlsx
+++ b/Combined_Broker_Trades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_0B4E91BF92AC475D621755F360FC431BDD4C924D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D556F7B5-4EBD-4361-A599-782AFB8E61BB}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_5852F3AC92AC475D6217554DF81DCB96D6CED442" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{940B216B-6C71-4B11-A517-12063A9FC82B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="77">
   <si>
     <t>Account Name</t>
   </si>
@@ -46,6 +46,15 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
     <t>Broker</t>
   </si>
   <si>
@@ -61,7 +70,13 @@
     <t>Buy</t>
   </si>
   <si>
-    <t>China AMC Select Money Market Fund</t>
+    <t>ChinaAMC Select Money Market Fund</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>HK0000502390</t>
   </si>
   <si>
     <t>FUTU</t>
@@ -70,7 +85,10 @@
     <t>07-02-2025</t>
   </si>
   <si>
-    <t>CSOP Hang Seng TECH Index ETF</t>
+    <t>CSOP HKD 1,000 5.0950 5,095.00 -5,112.44 Hang Seng TECH Index ETF</t>
+  </si>
+  <si>
+    <t>3033 HK</t>
   </si>
   <si>
     <t>10-02-2025</t>
@@ -97,6 +115,12 @@
     <t>Comgest Growth Europe EUR</t>
   </si>
   <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>IE00B5WN3467</t>
+  </si>
+  <si>
     <t>Vontobel</t>
   </si>
   <si>
@@ -106,12 +130,21 @@
     <t>iShares STOXX Europe 600 UCITS ETF (DE) 12.02.2026 Acquisto EUR</t>
   </si>
   <si>
+    <t>DE0002635307</t>
+  </si>
+  <si>
     <t>26-02-2026</t>
   </si>
   <si>
     <t>Novartis AG Namen 26.02.2026 Vendita CHF</t>
   </si>
   <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>CH0012005267</t>
+  </si>
+  <si>
     <t>Chaliki Jaya Ramesh</t>
   </si>
   <si>
@@ -124,7 +157,13 @@
     <t>22-04-2026</t>
   </si>
   <si>
-    <t>AAPL APPLE INC (SHS)</t>
+    <t>APPLE INC (SHS)</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>AAPL</t>
   </si>
   <si>
     <t>HSBC</t>
@@ -133,43 +172,37 @@
     <t>27-04-2026</t>
   </si>
   <si>
-    <t>NASA TEMA SPACE INNOVATORS (SHS)</t>
+    <t>TEMA SPACE INNOVATORS (SHS)</t>
+  </si>
+  <si>
+    <t>NASA</t>
   </si>
   <si>
     <t>28-04-2026</t>
   </si>
   <si>
-    <t>AXP AMERICAN EXPRESS CO. (SHS)</t>
+    <t>AMERICAN EXPRESS CO. (SHS)</t>
+  </si>
+  <si>
+    <t>AXP</t>
   </si>
   <si>
     <t>29-04-2026</t>
   </si>
   <si>
-    <t>XGT2023 HSBC GOLD TOKEN (TOZ)</t>
+    <t>HSBC GOLD TOKEN (TOZ)</t>
+  </si>
+  <si>
+    <t>XGT2023</t>
   </si>
   <si>
     <t>30-04-2026</t>
   </si>
   <si>
-    <t>GPIQ GOLDMAN SACHS NASDAQ-100 PRE (SHS)</t>
-  </si>
-  <si>
-    <t>Guillaume Boris Page</t>
-  </si>
-  <si>
-    <t>Guillaume Page</t>
-  </si>
-  <si>
-    <t>U***3268</t>
-  </si>
-  <si>
-    <t>08-05-2026</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>IBKR</t>
+    <t>GOLDMAN SACHS NASDAQ-100 PRE (SHS)</t>
+  </si>
+  <si>
+    <t>GPIQ</t>
   </si>
   <si>
     <t>Yao Mengqian</t>
@@ -184,28 +217,40 @@
     <t>19-05-2026</t>
   </si>
   <si>
-    <t>Yongdaauto</t>
+    <t>Yongdaqiche</t>
   </si>
   <si>
     <t>永達汽車</t>
   </si>
   <si>
-    <t>Jingdonghealth</t>
+    <t>3669 HK</t>
+  </si>
+  <si>
+    <t>Jingdongjiankang</t>
   </si>
   <si>
     <t>京東健康</t>
   </si>
   <si>
-    <t>Lanyueliang</t>
+    <t>6618 HK</t>
+  </si>
+  <si>
+    <t>Lanyueliangjituan</t>
   </si>
   <si>
     <t>藍月亮集團</t>
   </si>
   <si>
+    <t>6993 HK</t>
+  </si>
+  <si>
     <t>Meituan-w</t>
   </si>
   <si>
     <t>美團-W</t>
+  </si>
+  <si>
+    <t>3690 HK</t>
   </si>
 </sst>
 </file>
@@ -568,16 +613,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="86" customWidth="1"/>
-    <col min="2" max="2" width="54.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" customWidth="1"/>
+    <col min="3" max="3" width="40.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,459 +650,538 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>29.590449</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>1000</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H4">
         <v>924.61605299999997</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>452.42411600000003</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>1076.117</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>700</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H8">
         <v>150</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H9">
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H11">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="J11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H12">
         <v>0.1</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H13">
         <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="J13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>65</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>500</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15">
         <v>50</v>
       </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15">
-        <v>500</v>
-      </c>
       <c r="I15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18">
-        <v>100</v>
-      </c>
-      <c r="I18" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
